--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484272_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484272_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5545</v>
+        <v>4.7748</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4843</v>
+        <v>5.1404</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0702</v>
+        <v>-0.3656</v>
       </c>
       <c r="G2" t="n">
         <v>3.7913</v>
@@ -610,13 +610,13 @@
         <v>3.3208</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7796999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.677</v>
+        <v>0.3331</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1027</v>
+        <v>-0.3331</v>
       </c>
       <c r="V2" t="n">
         <v>2.9369</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3</v>
+        <v>1.1016</v>
       </c>
       <c r="E3" t="n">
-        <v>0.464</v>
+        <v>-0.4756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.836</v>
+        <v>1.5773</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8641</v>
+        <v>0.1175</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2146</v>
+        <v>0.077</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3506</v>
+        <v>0.0405</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2453</v>
+        <v>0.0622</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3262</v>
+        <v>0.6958</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0809</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M3" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="N3" t="n">
         <v>-0.6188</v>
       </c>
-      <c r="N3" t="n">
-        <v>-0.8885</v>
-      </c>
       <c r="O3" t="n">
-        <v>0.2696</v>
+        <v>0.6741</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1055</v>
+        <v>-0.3246</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6274</v>
+        <v>-0.1471</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4781</v>
+        <v>-0.1775</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2772</v>
+        <v>0.3321</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7027</v>
+        <v>0.806</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7383999999999999</v>
+        <v>0.1606</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4411</v>
+        <v>0.6454</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1175</v>
+        <v>-0.8641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.077</v>
+        <v>-1.2146</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0405</v>
+        <v>0.3506</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0622</v>
+        <v>-0.2453</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6958</v>
+        <v>-0.3262</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0553</v>
+        <v>-0.6188</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6188</v>
+        <v>-0.8885</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6741</v>
+        <v>0.2696</v>
       </c>
       <c r="P4" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.3907</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.3674</v>
-      </c>
       <c r="S4" t="n">
-        <v>-0.7236</v>
+        <v>0.6115</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4099</v>
+        <v>0.324</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3137</v>
+        <v>0.2875</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2362</v>
+        <v>-0.0612</v>
       </c>
       <c r="E5" t="n">
-        <v>0.582</v>
+        <v>0.7842</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8182</v>
+        <v>-0.8454</v>
       </c>
       <c r="G5" t="n">
         <v>0.3818</v>
@@ -844,13 +844,13 @@
         <v>0.3907</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.618</v>
+        <v>-0.443</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3631</v>
+        <v>-0.1609</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2548</v>
+        <v>-0.2821</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2113</v>
+        <v>-0.7796</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2386</v>
+        <v>0.1659</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9728</v>
+        <v>-0.9455</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6278</v>
@@ -922,13 +922,13 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8375</v>
+        <v>-0.4058</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2751</v>
+        <v>0.1294</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5624</v>
+        <v>-0.5352</v>
       </c>
       <c r="V6" t="n">
         <v>0.2772</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7787</v>
+        <v>-1.4325</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4717</v>
+        <v>-0.3706</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.307</v>
+        <v>-1.0619</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0906</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3208</v>
+        <v>0.0255</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1294</v>
+        <v>0.2305</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4502</v>
+        <v>-0.205</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4686</v>
+        <v>-2.3201</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2205</v>
+        <v>-1.0932</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2481</v>
+        <v>-1.2269</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7915</v>
+        <v>-3.3734</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2377</v>
+        <v>-2.5907</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.7827</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3261</v>
+        <v>-1.0418</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2047</v>
+        <v>-0.5296</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1214</v>
+        <v>-0.5122</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1176</v>
+        <v>-2.3316</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4423</v>
+        <v>-2.0611</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6753</v>
+        <v>-0.2704</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7357</v>
+        <v>-0.0722</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0108</v>
+        <v>0.1439</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7248</v>
+        <v>-0.2161</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1638</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8433</v>
+        <v>-2.7853</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8616</v>
+        <v>-0.5644</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9817</v>
+        <v>-2.2209</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3734</v>
+        <v>-1.7915</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5907</v>
+        <v>-1.2377</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7827</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0418</v>
+        <v>0.3261</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5296</v>
+        <v>0.2047</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5122</v>
+        <v>0.1214</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3316</v>
+        <v>-2.1176</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0611</v>
+        <v>-1.4423</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2704</v>
+        <v>-0.6753</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3441</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5954</v>
+        <v>-1.0524</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6244</v>
+        <v>-0.3548</v>
       </c>
       <c r="U9" t="n">
-        <v>0.029</v>
+        <v>-0.6976</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8463</v>
+        <v>-2.9784</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7435</v>
+        <v>-2.1479</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1029</v>
+        <v>-0.8305</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0225</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0192</v>
+        <v>-0.1513</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8778</v>
+        <v>0.4733</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.897</v>
+        <v>-0.6246</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0539</v>
+        <v>-3.0073</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5061</v>
+        <v>-2.405</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9666</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1106</v>
+        <v>-0.064</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1315</v>
+        <v>0.077</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9648</v>
+        <v>-3.8946</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0665</v>
+        <v>-0.2688</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8982</v>
+        <v>-3.6259</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3966</v>
@@ -1390,13 +1390,13 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9821</v>
+        <v>-0.912</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0108</v>
+        <v>-0.2131</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.6989</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8802</v>
+        <v>-4.8469</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1475</v>
+        <v>-4.087</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7327</v>
+        <v>-0.76</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0869</v>
@@ -1468,13 +1468,13 @@
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7115</v>
+        <v>-0.6782</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3878</v>
+        <v>-0.3272</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3237</v>
+        <v>-0.3509</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2772</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.7261</v>
+        <v>-15.4235</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.464099999999999</v>
+        <v>-5.1614</v>
       </c>
       <c r="F14" t="n">
         <v>-10.2622</v>
@@ -1546,13 +1546,13 @@
         <v>17.5809</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.769200000000001</v>
+        <v>-3.4665</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01239999999999986</v>
+        <v>0.2901</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.7566</v>
+        <v>-3.7565</v>
       </c>
       <c r="V14" t="n">
         <v>1.9955</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9779</v>
+        <v>8.0154</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8544</v>
+        <v>5.6522</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1235</v>
+        <v>2.3632</v>
       </c>
       <c r="G15" t="n">
         <v>3.7738</v>
@@ -1624,13 +1624,13 @@
         <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3409</v>
+        <v>1.3784</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5752</v>
+        <v>0.3729</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7657</v>
+        <v>1.0054</v>
       </c>
       <c r="V15" t="n">
         <v>1.4959</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3784</v>
+        <v>6.1343</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8452</v>
+        <v>3.1486</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5331</v>
+        <v>2.9857</v>
       </c>
       <c r="G16" t="n">
         <v>6.5225</v>
@@ -1702,13 +1702,13 @@
         <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0715</v>
+        <v>1.8275</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0359</v>
+        <v>0.3392</v>
       </c>
       <c r="U16" t="n">
-        <v>2.0356</v>
+        <v>1.4882</v>
       </c>
       <c r="V16" t="n">
         <v>1.4959</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5856</v>
+        <v>4.1341</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6982</v>
+        <v>2.5971</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8874</v>
+        <v>1.537</v>
       </c>
       <c r="G17" t="n">
         <v>3.0838</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8843</v>
+        <v>1.4327</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6962</v>
+        <v>0.5951</v>
       </c>
       <c r="U17" t="n">
-        <v>0.188</v>
+        <v>0.8376</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1638</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6479</v>
+        <v>2.8441</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9547</v>
+        <v>0.9398</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.3068</v>
+        <v>1.9043</v>
       </c>
       <c r="G18" t="n">
-        <v>3.9808</v>
+        <v>1.8371</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1681</v>
+        <v>0.3671</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1873</v>
+        <v>1.47</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2796</v>
+        <v>1.7128</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1177</v>
+        <v>-0.1625</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1619</v>
+        <v>1.8752</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2988</v>
+        <v>0.1243</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0504</v>
+        <v>0.5296</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3492</v>
+        <v>-0.4052</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1043</v>
+        <v>-0.1651</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9606</v>
+        <v>0.2037</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8563</v>
+        <v>-0.3688</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.0466</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5458</v>
+        <v>1.8323</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9398</v>
+        <v>1.8988</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6061</v>
+        <v>-0.0665</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8371</v>
+        <v>2.7706</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3671</v>
+        <v>0.6524</v>
       </c>
       <c r="I19" t="n">
-        <v>1.47</v>
+        <v>2.1182</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7128</v>
+        <v>4.0791</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1625</v>
+        <v>0.8813</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8752</v>
+        <v>3.1978</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1243</v>
+        <v>-1.3085</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5296</v>
+        <v>-0.2289</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4052</v>
+        <v>-1.0795</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1721</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4633</v>
+        <v>0.7883</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2037</v>
+        <v>0.7499</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.667</v>
+        <v>0.0384</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.764</v>
+        <v>1.2802</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2921</v>
+        <v>4.2357</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5281</v>
+        <v>-2.9555</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7706</v>
+        <v>3.9808</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6524</v>
+        <v>5.1681</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1182</v>
+        <v>-1.1873</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0791</v>
+        <v>5.2796</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8813</v>
+        <v>5.1177</v>
       </c>
       <c r="L20" t="n">
-        <v>3.1978</v>
+        <v>0.1619</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3085</v>
+        <v>-1.2988</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2289</v>
+        <v>0.0504</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>-1.3492</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2801</v>
+        <v>0.7367</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1432</v>
+        <v>1.2417</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4232</v>
+        <v>-0.5049</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5545</v>
+        <v>-3.0466</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4496</v>
+        <v>-0.2072</v>
       </c>
       <c r="E21" t="n">
         <v>-0.6752</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2256</v>
+        <v>0.468</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9218</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0319</v>
+        <v>0.2105</v>
       </c>
       <c r="T21" t="n">
         <v>0.2642</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2961</v>
+        <v>-0.0537</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4874</v>
+        <v>-2.0211</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1777</v>
+        <v>-2.4699</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3097</v>
+        <v>0.4488</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7548</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7874</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5447</v>
+        <v>0.1631</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2427</v>
+        <v>0.5158</v>
       </c>
       <c r="V22" t="n">
         <v>0.0549</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2365</v>
+        <v>-3.5896</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4693</v>
+        <v>-5.0648</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2328</v>
+        <v>1.4752</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3627</v>
@@ -2248,13 +2248,13 @@
         <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0692</v>
+        <v>-0.4223</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5777</v>
+        <v>-0.1732</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4915</v>
+        <v>-0.2491</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.7261</v>
+        <v>18.4225</v>
       </c>
       <c r="E24" t="n">
-        <v>10.2622</v>
+        <v>10.2623</v>
       </c>
       <c r="F24" t="n">
-        <v>5.463900000000001</v>
+        <v>8.1602</v>
       </c>
       <c r="G24" t="n">
         <v>14.9293</v>
@@ -2296,7 +2296,7 @@
         <v>14.9272</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002100000000000435</v>
+        <v>0.002100000000000879</v>
       </c>
       <c r="J24" t="n">
         <v>20.8725</v>
@@ -2308,13 +2308,13 @@
         <v>4.7277</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.943300000000001</v>
+        <v>-5.9433</v>
       </c>
       <c r="N24" t="n">
         <v>-1.2175</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.7256</v>
+        <v>-4.725600000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-0.9767000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>16.6042</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7691</v>
+        <v>6.465599999999999</v>
       </c>
       <c r="T24" t="n">
         <v>3.7566</v>
       </c>
       <c r="U24" t="n">
-        <v>0.01250000000000046</v>
+        <v>2.7089</v>
       </c>
       <c r="V24" t="n">
         <v>-1.9954</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484272_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484272_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1016</v>
+        <v>1.214</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4756</v>
+        <v>1.214</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5773</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1175</v>
+        <v>1.214</v>
       </c>
       <c r="H3" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0405</v>
+        <v>1.214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0622</v>
+        <v>1.214</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6958</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0553</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6188</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3246</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1471</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1775</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.806</v>
+        <v>1.1016</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1606</v>
+        <v>-0.4756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6454</v>
+        <v>1.5773</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8641</v>
+        <v>0.1175</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2146</v>
+        <v>0.077</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3506</v>
+        <v>0.0405</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2453</v>
+        <v>0.0622</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3262</v>
+        <v>0.6958</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0809</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M4" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="N4" t="n">
         <v>-0.6188</v>
       </c>
-      <c r="N4" t="n">
-        <v>-0.8885</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.2696</v>
+        <v>0.6741</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6115</v>
+        <v>-0.3246</v>
       </c>
       <c r="T4" t="n">
-        <v>0.324</v>
+        <v>-0.1471</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2875</v>
+        <v>-0.1775</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2772</v>
+        <v>0.3321</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +819,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0612</v>
+        <v>0.614</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7842</v>
+        <v>0.614</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8454</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3818</v>
+        <v>0.614</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5081</v>
+        <v>0.614</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8899</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3358</v>
+        <v>0.614</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0409</v>
+        <v>0.614</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2949</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.954</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.549</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.443</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1609</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -860,12 +880,17 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7796</v>
+        <v>0.499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1659</v>
+        <v>-0.1463</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9455</v>
+        <v>0.6454</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6278</v>
+        <v>-1.1711</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6388</v>
+        <v>-1.5216</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0111</v>
+        <v>0.3506</v>
       </c>
       <c r="J6" t="n">
-        <v>0.15</v>
+        <v>-0.5522</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2663</v>
+        <v>-0.6332</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4163</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7777</v>
+        <v>-0.6188</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3725</v>
+        <v>-0.8885</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4052</v>
+        <v>0.2696</v>
       </c>
       <c r="P6" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.3907</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3674</v>
-      </c>
       <c r="S6" t="n">
-        <v>-0.4058</v>
+        <v>0.6115</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1294</v>
+        <v>0.324</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5352</v>
+        <v>0.2875</v>
       </c>
       <c r="V6" t="n">
         <v>0.2772</v>
@@ -938,12 +963,17 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4325</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3706</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0619</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0906</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>0.638</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7286</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3523</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9455</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4429</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3075</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0255</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2305</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.205</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3201</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0932</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2269</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3734</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.5907</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7827</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0418</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5296</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5122</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3316</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0611</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2704</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0722</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1439</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2161</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7853</v>
+        <v>-0.7796</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5644</v>
+        <v>0.1659</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2209</v>
+        <v>-0.9455</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7915</v>
+        <v>-1.6278</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2377</v>
+        <v>-2.6388</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5538999999999999</v>
+        <v>1.0111</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3261</v>
+        <v>0.15</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2047</v>
+        <v>-1.2663</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1214</v>
+        <v>1.4163</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1176</v>
+        <v>-1.7777</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4423</v>
+        <v>-1.3725</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6753</v>
+        <v>-0.4052</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0524</v>
+        <v>-0.4058</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3548</v>
+        <v>0.1294</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6976</v>
+        <v>-0.5352</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1234,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9784</v>
+        <v>-1.2751</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1479</v>
+        <v>-0.4297</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8305</v>
+        <v>-0.8454</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0225</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8338</v>
+        <v>-0.5081</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1887</v>
+        <v>-0.3241</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6445</v>
+        <v>0.1219</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5912</v>
+        <v>0.0409</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0533</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3779</v>
+        <v>-0.954</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2425</v>
+        <v>-0.549</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1354</v>
+        <v>-0.4051</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1513</v>
+        <v>-0.443</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4733</v>
+        <v>-0.1609</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6246</v>
+        <v>-0.2821</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1250,12 +1295,17 @@
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MASLLORENS MANRIQUE</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1317,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0073</v>
+        <v>-2.0465</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.405</v>
+        <v>-0.9845</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.0619</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9666</v>
+        <v>-0.7045</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7933</v>
+        <v>0.0241</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1733</v>
+        <v>-0.7286</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2873</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6536</v>
+        <v>1.3315</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6793</v>
+        <v>-1.4429</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1397</v>
+        <v>-1.3075</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5397</v>
+        <v>-0.1354</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.064</v>
+        <v>0.0255</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.141</v>
+        <v>0.2305</v>
       </c>
       <c r="U11" t="n">
-        <v>0.077</v>
+        <v>-0.205</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1328,12 +1378,17 @@
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8946</v>
+        <v>-2.3201</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2688</v>
+        <v>-1.0932</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6259</v>
+        <v>-1.2269</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3966</v>
+        <v>-3.3734</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7337</v>
+        <v>-2.5907</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3371</v>
+        <v>-0.7827</v>
       </c>
       <c r="J12" t="n">
-        <v>2.0931</v>
+        <v>-1.0418</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.403</v>
+        <v>-0.5296</v>
       </c>
       <c r="L12" t="n">
-        <v>2.496</v>
+        <v>-0.5122</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.4897</v>
+        <v>-2.3316</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.3308</v>
+        <v>-2.0611</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1589</v>
+        <v>-0.2704</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.912</v>
+        <v>-0.0722</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2131</v>
+        <v>0.1439</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6989</v>
+        <v>-0.2161</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8469</v>
+        <v>-2.7853</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.087</v>
+        <v>-0.5644</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.76</v>
+        <v>-2.2209</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.0869</v>
+        <v>-1.7915</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6058</v>
+        <v>-1.2377</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.481</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4156</v>
+        <v>0.3261</v>
       </c>
       <c r="K13" t="n">
-        <v>0.66</v>
+        <v>0.2047</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0756</v>
+        <v>0.1214</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6712</v>
+        <v>-2.1176</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2658</v>
+        <v>-1.4423</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4054</v>
+        <v>-0.6753</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3441</v>
+        <v>-1.3674</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6782</v>
+        <v>-1.0524</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3272</v>
+        <v>-0.3548</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3509</v>
+        <v>-0.6976</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,385 +1566,406 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.4235</v>
+        <v>-2.9784</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.1614</v>
+        <v>-2.1479</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.2622</v>
+        <v>-0.8305</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.9294</v>
+        <v>-3.0225</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.9273</v>
+        <v>-2.8338</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.001899999999999569</v>
+        <v>-0.1887</v>
       </c>
       <c r="J14" t="n">
-        <v>5.943100000000001</v>
+        <v>-1.6445</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2175</v>
+        <v>-1.5912</v>
       </c>
       <c r="L14" t="n">
-        <v>4.7256</v>
+        <v>-0.0533</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.8722</v>
+        <v>-1.3779</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.1448</v>
+        <v>-1.2425</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.727600000000001</v>
+        <v>-0.1354</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.6041</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>17.5809</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.4665</v>
+        <v>-0.1513</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2901</v>
+        <v>0.4733</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.7565</v>
+        <v>-0.6246</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9955</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>5.2095</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.214</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>A. MASLLORENS MANRIQUE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.0154</v>
+        <v>-3.0073</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6522</v>
+        <v>-2.405</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3632</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7738</v>
+        <v>-1.9666</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6524</v>
+        <v>-0.7933</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1214</v>
+        <v>-1.1733</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4829</v>
+        <v>-1.2873</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6864</v>
+        <v>-0.6536</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7965</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7091</v>
+        <v>-0.6793</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.034</v>
+        <v>-0.1397</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6751</v>
+        <v>-0.5397</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3784</v>
+        <v>-0.064</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3729</v>
+        <v>-0.141</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0054</v>
+        <v>0.077</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1343</v>
+        <v>-3.8946</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1486</v>
+        <v>-0.2688</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9857</v>
+        <v>-3.6259</v>
       </c>
       <c r="G16" t="n">
-        <v>6.5225</v>
+        <v>-2.3966</v>
       </c>
       <c r="H16" t="n">
-        <v>3.272</v>
+        <v>-2.7337</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2505</v>
+        <v>0.3371</v>
       </c>
       <c r="J16" t="n">
-        <v>6.8965</v>
+        <v>2.0931</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6454</v>
+        <v>-0.403</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2511</v>
+        <v>2.496</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3741</v>
+        <v>-4.4897</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3735</v>
+        <v>-2.3308</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-2.1589</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.7115</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.8603</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8275</v>
+        <v>-0.912</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3392</v>
+        <v>-0.2131</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4882</v>
+        <v>-0.6989</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1341</v>
+        <v>-5.1539</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5971</v>
+        <v>-4.3939</v>
       </c>
       <c r="F17" t="n">
-        <v>1.537</v>
+        <v>-0.76</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0838</v>
+        <v>-4.3938</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4221</v>
+        <v>-1.9128</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6617</v>
+        <v>-2.481</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9787</v>
+        <v>-1.7226</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3164</v>
+        <v>0.353</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6623</v>
+        <v>-2.0756</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1051</v>
+        <v>-2.6712</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1057</v>
+        <v>-2.2658</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.4054</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-2.3441</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4327</v>
+        <v>-0.6782</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5951</v>
+        <v>-0.3272</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8376</v>
+        <v>-0.3509</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1638</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1638</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8441</v>
+        <v>-15.4234</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9398</v>
+        <v>-5.161000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9043</v>
+        <v>-10.2622</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8371</v>
+        <v>-14.9292</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3671</v>
+        <v>-14.9272</v>
       </c>
       <c r="I18" t="n">
-        <v>1.47</v>
+        <v>-0.001900000000000013</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7128</v>
+        <v>5.9434</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1625</v>
+        <v>1.217499999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8752</v>
+        <v>4.7256</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1243</v>
+        <v>-20.8722</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5296</v>
+        <v>-16.1448</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4052</v>
+        <v>-4.7276</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>0.9766999999999998</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-16.6041</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>17.5809</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1651</v>
+        <v>-3.4665</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2037</v>
+        <v>0.2901</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3688</v>
+        <v>-3.7565</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.9955</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>5.2095</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
-      </c>
+        <v>-3.214</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CRUZ URBANEJA</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8323</v>
+        <v>8.0154</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8988</v>
+        <v>5.6522</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0665</v>
+        <v>2.3632</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7706</v>
+        <v>3.7738</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6524</v>
+        <v>3.6524</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1182</v>
+        <v>0.1214</v>
       </c>
       <c r="J19" t="n">
-        <v>4.0791</v>
+        <v>4.4829</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8813</v>
+        <v>3.6864</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1978</v>
+        <v>0.7965</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3085</v>
+        <v>-0.7091</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2289</v>
+        <v>-0.034</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0795</v>
+        <v>-0.6751</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7883</v>
+        <v>1.3784</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7499</v>
+        <v>0.3729</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0384</v>
+        <v>1.0054</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5545</v>
+        <v>1.4959</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2802</v>
+        <v>6.1343</v>
       </c>
       <c r="E20" t="n">
-        <v>4.2357</v>
+        <v>3.1486</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9555</v>
+        <v>2.9857</v>
       </c>
       <c r="G20" t="n">
-        <v>3.9808</v>
+        <v>6.5225</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1681</v>
+        <v>3.272</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1873</v>
+        <v>3.2505</v>
       </c>
       <c r="J20" t="n">
-        <v>5.2796</v>
+        <v>6.8965</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1177</v>
+        <v>3.6454</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1619</v>
+        <v>3.2511</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2988</v>
+        <v>-0.3741</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0504</v>
+        <v>-0.3735</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3492</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-3.7115</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-5.8603</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7367</v>
+        <v>1.8275</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2417</v>
+        <v>0.3392</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5049</v>
+        <v>1.4882</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.0466</v>
+        <v>1.4959</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>1.7731</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2143,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2072</v>
+        <v>4.1341</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6752</v>
+        <v>2.5971</v>
       </c>
       <c r="F21" t="n">
-        <v>0.468</v>
+        <v>1.537</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9218</v>
+        <v>3.0838</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1279</v>
+        <v>2.4221</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0497</v>
+        <v>0.6617</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0373</v>
+        <v>2.9787</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4121</v>
+        <v>2.3164</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3748</v>
+        <v>0.6623</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9591</v>
+        <v>0.1051</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2842</v>
+        <v>0.1057</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P21" t="n">
         <v>0.7814</v>
@@ -2092,28 +2188,33 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2105</v>
+        <v>1.4327</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2642</v>
+        <v>0.5951</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0537</v>
+        <v>0.8376</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>-1.1638</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0211</v>
+        <v>2.8441</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4699</v>
+        <v>0.9398</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4488</v>
+        <v>1.9043</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7548</v>
+        <v>1.8371</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.395</v>
+        <v>0.3671</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3598</v>
+        <v>1.47</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6562</v>
+        <v>1.7128</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1637</v>
+        <v>-0.1625</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.82</v>
+        <v>1.8752</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0986</v>
+        <v>0.1243</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5587</v>
+        <v>0.5296</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5399</v>
+        <v>-0.4052</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6788999999999999</v>
+        <v>-0.1651</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1631</v>
+        <v>0.2037</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5158</v>
+        <v>-0.3688</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0549</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>M. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5896</v>
+        <v>1.8323</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0648</v>
+        <v>1.8988</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4752</v>
+        <v>-0.0665</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3627</v>
+        <v>2.7706</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3398</v>
+        <v>0.6524</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0229</v>
+        <v>2.1182</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9382</v>
+        <v>4.0791</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9159</v>
+        <v>0.8813</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0223</v>
+        <v>3.1978</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4245</v>
+        <v>-1.3085</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4239</v>
+        <v>-0.2289</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.0795</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4223</v>
+        <v>0.7883</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1732</v>
+        <v>0.7499</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2491</v>
+        <v>0.0384</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,401 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>1.2802</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.2357</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.9555</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.9808</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5.1681</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.1873</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.2796</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.1177</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.2988</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.3492</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.7367</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.2417</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.5049</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-3.0466</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>N. DEL VAL GARCIA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.2072</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.6752</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.9218</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.1279</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.0497</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.4121</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.3748</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.9591</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2842</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.0537</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J. CANAL FERRER</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.0211</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.4699</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.7548</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.395</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.3598</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.6562</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.0986</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.5158</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. RIERA PERETO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.5896</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-5.0648</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.4752</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.3627</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.3398</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2.0229</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-2.9382</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.9159</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.4245</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.4239</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.4223</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.1732</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2491</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484272_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>18.4225</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E28" t="n">
         <v>10.2623</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F28" t="n">
         <v>8.1602</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G28" t="n">
         <v>14.9293</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H28" t="n">
         <v>14.9272</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I28" t="n">
         <v>0.002100000000000879</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J28" t="n">
         <v>20.8725</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K28" t="n">
         <v>16.1446</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L28" t="n">
         <v>4.7277</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M28" t="n">
         <v>-5.9433</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N28" t="n">
         <v>-1.2175</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-4.725600000000001</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P28" t="n">
         <v>-0.9767000000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q28" t="n">
         <v>-17.5807</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>16.6042</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S28" t="n">
         <v>6.465599999999999</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T28" t="n">
         <v>3.7566</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U28" t="n">
         <v>2.7089</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V28" t="n">
         <v>-1.9954</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W28" t="n">
         <v>3.2141</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X28" t="n">
         <v>-5.2095</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
